--- a/EasyFramework.NET/EasyFramework.Excel/Settings/#_Settings.xlsx
+++ b/EasyFramework.NET/EasyFramework.Excel/Settings/#_Settings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11900" windowHeight="15070" firstSheet="1"/>
+    <workbookView windowHeight="17680" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>Key</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>ClassSuffix</t>
+  </si>
+  <si>
+    <t>OutputDataFileName</t>
+  </si>
+  <si>
+    <t>ConfigData.bytes</t>
   </si>
   <si>
     <t>OutputScriptPath</t>
@@ -1082,10 +1088,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.8333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.8916666666667" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.9166666666667" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
@@ -1175,31 +1181,39 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" ht="39" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="4">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="39" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>21</v>
+      <c r="C16" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1236,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1233,10 +1247,10 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1244,7 +1258,7 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
@@ -1252,7 +1266,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1269,22 +1283,22 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:3">
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2"/>
     </row>
